--- a/results/job_matches_2026-05-16.xlsx
+++ b/results/job_matches_2026-05-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,35 +538,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior DJI Dock 2 / Cloud API Integration Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Scala, Kafka</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76df9b54cd60a601</t>
+          <t>https://www.indeed.com/viewjob?jk=f4968d826aaf9e4d</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5902e7f954c993c8</t>
+          <t>https://www.indeed.com/viewjob?jk=76df9b54cd60a601</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e578397657651918</t>
+          <t>https://www.indeed.com/viewjob?jk=5902e7f954c993c8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer &amp; Database Administrator II</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3MD Inc.</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala, Kafka</t>
+          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e15d496bc7bea2</t>
+          <t>https://www.indeed.com/viewjob?jk=e578397657651918</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Applications Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Medallion Architecture, Hadoop, Hive, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Blob Storage, Oracle, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=430b7dc361a7ba29</t>
+          <t>https://www.indeed.com/viewjob?jk=40cf2df7dd84b43b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Medallion Architecture, Hadoop, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62ca3c3ce12832cd</t>
+          <t>https://www.indeed.com/viewjob?jk=430b7dc361a7ba29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Applications Developer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Blob Storage, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40cf2df7dd84b43b</t>
+          <t>https://www.indeed.com/viewjob?jk=62ca3c3ce12832cd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Sr Advanced Cloud Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=998e98c766a8e459</t>
+          <t>https://www.indeed.com/viewjob?jk=b77fa4bb580f7b02</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Software Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Fluency</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e373e64c1d569cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IT Full Stack Developer, Commercial</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6dd7576289a4b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=e373e64c1d569cf9</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Southern Trust Insurance Company</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Macon, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0200a14e25dfc13</t>
+          <t>https://www.indeed.com/viewjob?jk=37b659efacce143d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Southern Trust Insurance Company</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Macon, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b659efacce143d</t>
+          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>RDS, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c37fa14593f151f</t>
+          <t>https://www.indeed.com/viewjob?jk=2e2a80dff0ea8242</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ELT</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a37858bb8ebc527</t>
+          <t>https://www.indeed.com/viewjob?jk=3de44fa63b4b67d2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Architect and Database Engineer (Hands on)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Stratus</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,29 +1781,29 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Hive, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
+          <t>https://www.indeed.com/viewjob?jk=927d413c04d6f9fa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Architect and Database Engineer (Hands on)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Stratus</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1812,11 +1812,11 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Hive, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927d413c04d6f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=c55dd3f9232ba677</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c55dd3f9232ba677</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd6dc8c3a5470cf</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Engineer II, Cloud &amp; Web Systems Software</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Masimo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6dc8c3a5470cf</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
         </is>
       </c>
     </row>
@@ -2183,25 +2183,25 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Data Engineer – Remote / Flexible</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>S3, RDS, Kafka, Snowflake, Time Travel, clustering keys, ETL, ELT, Tableau, Tableau Server</t>
+          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df16bce6ff0b45b9</t>
+          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Verkada</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c010146ae6d1df</t>
+          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Software</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
+          <t>https://www.indeed.com/viewjob?jk=63c010146ae6d1df</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer – Remote / Flexible</t>
+          <t>Senior Data Engineer - Software</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr Software Developer (Data Agents)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5731aade3047f8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Software Developer (Data Agents)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,69 +2586,69 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
+          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
+          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Sr. Platform Engineer (AWS/Call Center)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>RealTruck</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
+          <t>https://www.indeed.com/viewjob?jk=5eacf8e440d50fc0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer (AWS/Call Center)</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RealTruck</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eacf8e440d50fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=b7976715069e9a69</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7976715069e9a69</t>
+          <t>https://www.indeed.com/viewjob?jk=4e1a685db36736a9</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e1a685db36736a9</t>
+          <t>https://www.indeed.com/viewjob?jk=3c03120ae5d030db</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c03120ae5d030db</t>
+          <t>https://www.indeed.com/viewjob?jk=311bc1fef3da325e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Data &amp; AI Solution Architect - AWS Cloud Platforms</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311bc1fef3da325e</t>
+          <t>https://www.indeed.com/viewjob?jk=811dd7a3eedaa479</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Technical Product Owner II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Proscia</t>
+          <t>Computer Services Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,42 +2901,42 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Spark, Snowflake, Oracle, Data Modeling, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb7931c11fca7d19</t>
+          <t>https://www.indeed.com/viewjob?jk=844a388f6929d4ff</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data &amp; AI Solution Architect - AWS Cloud Platforms</t>
+          <t>Senior Data Scientist + Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NEOTAX</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Databricks</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=811dd7a3eedaa479</t>
+          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Technical Product Owner II</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Computer Services Inc.</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Snowflake, Oracle, Data Modeling, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=844a388f6929d4ff</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4f8692b1b780d5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer (Contract-to-Hire, Part-Time)</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ZENO Group</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ed8a390361bf1a</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b00c104b625fb</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Intellirent</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Roanoke, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
+          <t>https://www.indeed.com/viewjob?jk=411c82ee69f9645d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d956b2a0c9bb45a</t>
+          <t>https://www.indeed.com/viewjob?jk=9661a8215828cb59</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Consultant, Cloud Solutions</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Burwood Group</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
+          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer (Contract-to-Hire, Part-Time)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ZENO Group</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d73094e1a0a14b40</t>
+          <t>https://www.indeed.com/viewjob?jk=15ed8a390361bf1a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Intellirent</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>Roanoke, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
+          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Scientist + Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NEOTAX</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
+          <t>https://www.indeed.com/viewjob?jk=0d956b2a0c9bb45a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Consultant, Cloud Solutions</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Burwood Group</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4f8692b1b780d5</t>
+          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b00c104b625fb</t>
+          <t>https://www.indeed.com/viewjob?jk=d73094e1a0a14b40</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=411c82ee69f9645d</t>
+          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9661a8215828cb59</t>
+          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
+          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Sr. Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, NoSQL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
+          <t>https://www.indeed.com/viewjob?jk=6f160aadc0d3bdd6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5d88d53c2ff675</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cloud Services Database Specialist</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Centric Software</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Campbell, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f68db530cad44d37</t>
+          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Machine Learning</t>
+          <t>Principle Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, NoSQL, ELT, CI/CD, Docker</t>
+          <t>RDS, Azure, Blob Storage, Dataflow, Scala, SQL Server, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f160aadc0d3bdd6</t>
+          <t>https://www.indeed.com/viewjob?jk=e26a94c5a6adceae</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
+          <t>Data Specialist</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Paramount Streaming</t>
+          <t>via</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, Azure, PostgreSQL, ETL, ELT, dbt, pytest, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5d88d53c2ff675</t>
+          <t>https://www.indeed.com/viewjob?jk=bc8c37d3b685ec0e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Salesforce Software Engineer</t>
+          <t>Data Integration Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tractor Zoom, Inc.</t>
+          <t>Austin Community College</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3dd39f8b74b55a</t>
+          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Stelo Support Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Onebridge</t>
+          <t>STELO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
+          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Stelo Support Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>STELO</t>
+          <t>Intuitive (Intuitive Surgical)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,147 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Daniels Health</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64d55709d1731472</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Principle Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Paradigm</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Virginia Beach, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Blob Storage, Dataflow, Scala, SQL Server, CI/CD, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e26a94c5a6adceae</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Data Specialist</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>via</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Somerville, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Azure, PostgreSQL, ETL, ELT, dbt, pytest, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8c37d3b685ec0e</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Data Integration Developer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Austin Community College</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=3677cf32b1561e4d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-16.xlsx
+++ b/results/job_matches_2026-05-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,25 +783,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Sr Advanced Cloud Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62ca3c3ce12832cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b77fa4bb580f7b02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Advanced Cloud Developer</t>
+          <t>FullStack AWS AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77fa4bb580f7b02</t>
+          <t>https://www.indeed.com/viewjob?jk=fe20ccdbad190f18</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FullStack AWS AI Engineer</t>
+          <t>AI Engineer (DFW Hybrid)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Data Modeling, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe20ccdbad190f18</t>
+          <t>https://www.indeed.com/viewjob?jk=44b6307f2370f7ba</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Engineer (DFW Hybrid)</t>
+          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Data Modeling, ELT, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44b6307f2370f7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=44dd55cd74d57902</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44dd55cd74d57902</t>
+          <t>https://www.indeed.com/viewjob?jk=07b73c3206a7c35a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b73c3206a7c35a</t>
+          <t>https://www.indeed.com/viewjob?jk=fd51f4466b978623</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Senior Software Engineer-Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>The Trade Desk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, CI/CD</t>
+          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd51f4466b978623</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbbb1cacaaeb3af</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbbb1cacaaeb3af</t>
+          <t>https://www.indeed.com/viewjob?jk=8c3dda8a9a898a72</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Data Engineer</t>
+          <t>Senior AWS Cloud Infrastructure Engineer (Terraform / IaC)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Trade Desk</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c3dda8a9a898a72</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff5ff5e83aa53c1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Infrastructure Engineer (Terraform / IaC)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Biamp Systems</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff5ff5e83aa53c1</t>
+          <t>https://www.indeed.com/viewjob?jk=619b21a83c2def71</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Biamp Systems</t>
+          <t>Fluency</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619b21a83c2def71</t>
+          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Software Engineer 2 ( Backend)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cb79ea92c31c11</t>
+          <t>https://www.indeed.com/viewjob?jk=020cd3f89e269314</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Software Engineer 2 ( Backend)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15643afd51a012f</t>
+          <t>https://www.indeed.com/viewjob?jk=bd22044f3d0a4060</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Fort Meyers</t>
+          <t>Software Engineer 2 ( Backend)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fort Myers, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f61b1f4473db23</t>
+          <t>https://www.indeed.com/viewjob?jk=54e3095eee752df8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer 2 ( Backend)</t>
+          <t>Senior DevOps &amp; Site Reliability Engineer - Americas</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Appspace</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=020cd3f89e269314</t>
+          <t>https://www.indeed.com/viewjob?jk=be33dcc3ef2e6cb9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer 2 ( Backend)</t>
+          <t>Databricks Architect | US</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Cuesta Partners</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd22044f3d0a4060</t>
+          <t>https://www.indeed.com/viewjob?jk=a549584a5dbc708e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer 2 ( Backend)</t>
+          <t>Site AI Engineer - Fort Meyers</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Myers, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e3095eee752df8</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f61b1f4473db23</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevOps &amp; Site Reliability Engineer - Americas</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Appspace</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be33dcc3ef2e6cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=96cb79ea92c31c11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Databricks Architect | US</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cuesta Partners</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a549584a5dbc708e</t>
+          <t>https://www.indeed.com/viewjob?jk=f15643afd51a012f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Platform</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fluency</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
+          <t>https://www.indeed.com/viewjob?jk=e373e64c1d569cf9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Senior Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e373e64c1d569cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=52e7d086f3b943f3</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e7d086f3b943f3</t>
+          <t>https://www.indeed.com/viewjob?jk=f717e7ca607998f2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Adhesives Research</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Glen Rock, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f717e7ca607998f2</t>
+          <t>https://www.indeed.com/viewjob?jk=5351eb2f4c376213</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Adhesives Research</t>
+          <t>Southern Trust Insurance Company</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Glen Rock, PA, US USA</t>
+          <t>Macon, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5351eb2f4c376213</t>
+          <t>https://www.indeed.com/viewjob?jk=37b659efacce143d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Southern Trust Insurance Company</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Macon, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b659efacce143d</t>
+          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
+          <t>https://www.indeed.com/viewjob?jk=2e2a80dff0ea8242</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Architect and Database Engineer (Hands on)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Stratus</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Hive, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e2a80dff0ea8242</t>
+          <t>https://www.indeed.com/viewjob?jk=927d413c04d6f9fa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de44fa63b4b67d2</t>
+          <t>https://www.indeed.com/viewjob?jk=c55dd3f9232ba677</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Architect and Database Engineer (Hands on)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Stratus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Hive, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927d413c04d6f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd6dc8c3a5470cf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c55dd3f9232ba677</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe2438fb1b9d07</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Engineer II, Cloud &amp; Web Systems Software</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Masimo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6dc8c3a5470cf</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe2438fb1b9d07</t>
+          <t>https://www.indeed.com/viewjob?jk=b576f637ff969834</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Engineer II, Cloud &amp; Web Systems Software</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Masimo</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=179695ff545f1e20</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b576f637ff969834</t>
+          <t>https://www.indeed.com/viewjob?jk=41e7b2135c1ebf09</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179695ff545f1e20</t>
+          <t>https://www.indeed.com/viewjob?jk=d929fe14c4afbac2</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41e7b2135c1ebf09</t>
+          <t>https://www.indeed.com/viewjob?jk=dca030c7965ce41e</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d929fe14c4afbac2</t>
+          <t>https://www.indeed.com/viewjob?jk=5afcb01b26889c52</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca030c7965ce41e</t>
+          <t>https://www.indeed.com/viewjob?jk=ed2747917ef629b6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>S3, RDS, Kafka, Snowflake, Time Travel, clustering keys, ETL, ELT, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afcb01b26889c52</t>
+          <t>https://www.indeed.com/viewjob?jk=df16bce6ff0b45b9</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Engineer – Remote / Flexible</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed2747917ef629b6</t>
+          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer – Remote / Flexible</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Verkada</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Software</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Verkada</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
+          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Allworth Financial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c010146ae6d1df</t>
+          <t>https://www.indeed.com/viewjob?jk=23d2bdc3bf9a8a45</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Software</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd6d6bd7fa1196f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>SAP NS2 DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Allworth Financial</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d2bdc3bf9a8a45</t>
+          <t>https://www.indeed.com/viewjob?jk=1e077c2e8ed4afda</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer (ONSITE)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Teachers Federal Credit Union</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hauppauge, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Dimensional Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd6d6bd7fa1196f</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea4f50a56e2ea5d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SAP NS2 DevOps Engineer</t>
+          <t>AI Automation Developer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Yale New Haven Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Stratford, CT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e077c2e8ed4afda</t>
+          <t>https://www.indeed.com/viewjob?jk=f343549fb0b598c9</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer (ONSITE)</t>
+          <t>Business Intelligence Data Analyst - GPSC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Teachers Federal Credit Union</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hauppauge, NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Dimensional Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea4f50a56e2ea5d</t>
+          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Automation Developer II</t>
+          <t>Sr Software Developer (Data Agents)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Yale New Haven Health</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Stratford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f343549fb0b598c9</t>
+          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Analyst - GPSC</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,42 +2516,42 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
+          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Software Developer (Data Agents)</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,59 +2561,59 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
+          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>Sr. Platform Engineer (AWS/Call Center)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>RealTruck</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=5eacf8e440d50fc0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
+          <t>https://www.indeed.com/viewjob?jk=b7976715069e9a69</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer (AWS/Call Center)</t>
+          <t>Senior Software Engineer AI/Gen AI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RealTruck</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eacf8e440d50fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=4e1a685db36736a9</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7976715069e9a69</t>
+          <t>https://www.indeed.com/viewjob?jk=3c03120ae5d030db</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e1a685db36736a9</t>
+          <t>https://www.indeed.com/viewjob?jk=311bc1fef3da325e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Data &amp; AI Solution Architect - AWS Cloud Platforms</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c03120ae5d030db</t>
+          <t>https://www.indeed.com/viewjob?jk=811dd7a3eedaa479</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Technical Product Owner II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Computer Services Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Spark, Snowflake, Oracle, Data Modeling, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311bc1fef3da325e</t>
+          <t>https://www.indeed.com/viewjob?jk=844a388f6929d4ff</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data &amp; AI Solution Architect - AWS Cloud Platforms</t>
+          <t>Senior Data Scientist + Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NEOTAX</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Databricks</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=811dd7a3eedaa479</t>
+          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Technical Product Owner II</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Computer Services Inc.</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Snowflake, Oracle, Data Modeling, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=844a388f6929d4ff</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4f8692b1b780d5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Scientist + Machine Learning Engineer</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NEOTAX</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b00c104b625fb</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4f8692b1b780d5</t>
+          <t>https://www.indeed.com/viewjob?jk=411c82ee69f9645d</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b00c104b625fb</t>
+          <t>https://www.indeed.com/viewjob?jk=9661a8215828cb59</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3046,29 +3046,29 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=411c82ee69f9645d</t>
+          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Intellirent</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Roanoke, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9661a8215828cb59</t>
+          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,29 +3111,29 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
+          <t>https://www.indeed.com/viewjob?jk=0d956b2a0c9bb45a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer (Contract-to-Hire, Part-Time)</t>
+          <t>Consultant, Cloud Solutions</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ZENO Group</t>
+          <t>Burwood Group</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ed8a390361bf1a</t>
+          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Intellirent</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Roanoke, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
+          <t>https://www.indeed.com/viewjob?jk=d73094e1a0a14b40</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d956b2a0c9bb45a</t>
+          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Consultant, Cloud Solutions</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Burwood Group</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
+          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d73094e1a0a14b40</t>
+          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
+          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Sr. Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, NoSQL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
+          <t>https://www.indeed.com/viewjob?jk=6f160aadc0d3bdd6</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5d88d53c2ff675</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Machine Learning</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, NoSQL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f160aadc0d3bdd6</t>
+          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
+          <t>Principle Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Paramount Streaming</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Dataflow, Scala, SQL Server, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5d88d53c2ff675</t>
+          <t>https://www.indeed.com/viewjob?jk=e26a94c5a6adceae</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Stelo Support Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Onebridge</t>
+          <t>STELO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
+          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Principle Infrastructure Engineer</t>
+          <t>Stelo Support Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Paradigm</t>
+          <t>STELO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Dataflow, Scala, SQL Server, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26a94c5a6adceae</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Stelo Support Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>STELO</t>
+          <t>Intuitive (Intuitive Surgical)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3645,76 +3645,6 @@
         </is>
       </c>
       <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Stelo Support Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>STELO</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Intuitive (Intuitive Surgical)</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Peachtree Corners, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes, Git, Bitbucket</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3677cf32b1561e4d</t>
         </is>

--- a/results/job_matches_2026-05-16.xlsx
+++ b/results/job_matches_2026-05-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Educology Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76df9b54cd60a601</t>
+          <t>https://www.indeed.com/viewjob?jk=ea52f552407f8b0e</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5902e7f954c993c8</t>
+          <t>https://www.indeed.com/viewjob?jk=76df9b54cd60a601</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e578397657651918</t>
+          <t>https://www.indeed.com/viewjob?jk=5902e7f954c993c8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Full Stack Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, MongoDB, DynamoDB</t>
+          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894b0939d20a58ea</t>
+          <t>https://www.indeed.com/viewjob?jk=e578397657651918</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Engineer (DFW Hybrid)</t>
+          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Data Modeling, ELT, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44b6307f2370f7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=44dd55cd74d57902</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44dd55cd74d57902</t>
+          <t>https://www.indeed.com/viewjob?jk=07b73c3206a7c35a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b73c3206a7c35a</t>
+          <t>https://www.indeed.com/viewjob?jk=fd51f4466b978623</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Senior Software Engineer-Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>The Trade Desk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, CI/CD</t>
+          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd51f4466b978623</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbbb1cacaaeb3af</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbbb1cacaaeb3af</t>
+          <t>https://www.indeed.com/viewjob?jk=8c3dda8a9a898a72</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Data Engineer</t>
+          <t>Senior AWS Cloud Infrastructure Engineer (Terraform / IaC)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Trade Desk</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c3dda8a9a898a72</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff5ff5e83aa53c1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Infrastructure Engineer (Terraform / IaC)</t>
+          <t>Software Engineer 2 ( Backend)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff5ff5e83aa53c1</t>
+          <t>https://www.indeed.com/viewjob?jk=020cd3f89e269314</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer 2 ( Backend)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Biamp Systems</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619b21a83c2def71</t>
+          <t>https://www.indeed.com/viewjob?jk=bd22044f3d0a4060</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Platform</t>
+          <t>Software Engineer 2 ( Backend)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fluency</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
+          <t>https://www.indeed.com/viewjob?jk=54e3095eee752df8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer 2 ( Backend)</t>
+          <t>Senior DevOps &amp; Site Reliability Engineer - Americas</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Appspace</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=020cd3f89e269314</t>
+          <t>https://www.indeed.com/viewjob?jk=be33dcc3ef2e6cb9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer 2 ( Backend)</t>
+          <t>Databricks Architect | US</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Cuesta Partners</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd22044f3d0a4060</t>
+          <t>https://www.indeed.com/viewjob?jk=a549584a5dbc708e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer 2 ( Backend)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Biamp Systems</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
+          <t>AWS, IAM, Azure, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e3095eee752df8</t>
+          <t>https://www.indeed.com/viewjob?jk=619b21a83c2def71</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevOps &amp; Site Reliability Engineer - Americas</t>
+          <t>Software Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Appspace</t>
+          <t>Fluency</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be33dcc3ef2e6cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Databricks Architect | US</t>
+          <t>Site AI Engineer - Fort Meyers</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cuesta Partners</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Myers, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a549584a5dbc708e</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f61b1f4473db23</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Fort Meyers</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fort Myers, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f61b1f4473db23</t>
+          <t>https://www.indeed.com/viewjob?jk=96cb79ea92c31c11</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cb79ea92c31c11</t>
+          <t>https://www.indeed.com/viewjob?jk=f15643afd51a012f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Senior Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15643afd51a012f</t>
+          <t>https://www.indeed.com/viewjob?jk=52e7d086f3b943f3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Senior Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e373e64c1d569cf9</t>
+          <t>https://www.indeed.com/viewjob?jk=f717e7ca607998f2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Adhesives Research</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Glen Rock, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e7d086f3b943f3</t>
+          <t>https://www.indeed.com/viewjob?jk=5351eb2f4c376213</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Southern Trust Insurance Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Macon, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f717e7ca607998f2</t>
+          <t>https://www.indeed.com/viewjob?jk=37b659efacce143d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Adhesives Research</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Glen Rock, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5351eb2f4c376213</t>
+          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect and Database Engineer (Hands on)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Southern Trust Insurance Company</t>
+          <t>Stratus</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Macon, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,77 +1606,77 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Hive, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b659efacce143d</t>
+          <t>https://www.indeed.com/viewjob?jk=927d413c04d6f9fa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
+          <t>https://www.indeed.com/viewjob?jk=c55dd3f9232ba677</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,59 +1686,59 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e2a80dff0ea8242</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd6dc8c3a5470cf</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Architect and Database Engineer (Hands on)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Stratus</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Hive, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927d413c04d6f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe2438fb1b9d07</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Engineer II, Cloud &amp; Web Systems Software</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>Masimo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c55dd3f9232ba677</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6dc8c3a5470cf</t>
+          <t>https://www.indeed.com/viewjob?jk=b576f637ff969834</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe2438fb1b9d07</t>
+          <t>https://www.indeed.com/viewjob?jk=179695ff545f1e20</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Engineer II, Cloud &amp; Web Systems Software</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Masimo</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=41e7b2135c1ebf09</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b576f637ff969834</t>
+          <t>https://www.indeed.com/viewjob?jk=d929fe14c4afbac2</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179695ff545f1e20</t>
+          <t>https://www.indeed.com/viewjob?jk=dca030c7965ce41e</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41e7b2135c1ebf09</t>
+          <t>https://www.indeed.com/viewjob?jk=5afcb01b26889c52</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d929fe14c4afbac2</t>
+          <t>https://www.indeed.com/viewjob?jk=ed2747917ef629b6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>S3, RDS, Kafka, Snowflake, Time Travel, clustering keys, ETL, ELT, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca030c7965ce41e</t>
+          <t>https://www.indeed.com/viewjob?jk=df16bce6ff0b45b9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Engineer – Remote / Flexible</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Sparklebulb</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afcb01b26889c52</t>
+          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Verkada</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed2747917ef629b6</t>
+          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Senior Data Engineer - Software</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>S3, RDS, Kafka, Snowflake, Time Travel, clustering keys, ETL, ELT, Tableau, Tableau Server</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df16bce6ff0b45b9</t>
+          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer – Remote / Flexible</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Allworth Financial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=23d2bdc3bf9a8a45</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Verkada</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd6d6bd7fa1196f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Software</t>
+          <t>SAP NS2 DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
+          <t>https://www.indeed.com/viewjob?jk=1e077c2e8ed4afda</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Automation Developer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Allworth Financial</t>
+          <t>Yale New Haven Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Stratford, CT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d2bdc3bf9a8a45</t>
+          <t>https://www.indeed.com/viewjob?jk=f343549fb0b598c9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Business Intelligence Data Analyst - GPSC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd6d6bd7fa1196f</t>
+          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SAP NS2 DevOps Engineer</t>
+          <t>Sr Software Developer (Data Agents)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e077c2e8ed4afda</t>
+          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer (ONSITE)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Teachers Federal Credit Union</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hauppauge, NY, US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,157 +2376,157 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Dimensional Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea4f50a56e2ea5d</t>
+          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Automation Developer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Yale New Haven Health</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Stratford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f343549fb0b598c9</t>
+          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Analyst - GPSC</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Software Developer (Data Agents)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
+          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
+          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Technical Product Owner II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Computer Services Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Spark, Snowflake, Oracle, Data Modeling, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7976715069e9a69</t>
+          <t>https://www.indeed.com/viewjob?jk=844a388f6929d4ff</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Senior Data Scientist + Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>NEOTAX</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e1a685db36736a9</t>
+          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c03120ae5d030db</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4f8692b1b780d5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer AI/Gen AI</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311bc1fef3da325e</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b00c104b625fb</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data &amp; AI Solution Architect - AWS Cloud Platforms</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Databricks</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=811dd7a3eedaa479</t>
+          <t>https://www.indeed.com/viewjob?jk=411c82ee69f9645d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Technical Product Owner II</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Computer Services Inc.</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Snowflake, Oracle, Data Modeling, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=844a388f6929d4ff</t>
+          <t>https://www.indeed.com/viewjob?jk=9661a8215828cb59</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Scientist + Machine Learning Engineer</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NEOTAX</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
+          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Intellirent</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Roanoke, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4f8692b1b780d5</t>
+          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,19 +2946,19 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b00c104b625fb</t>
+          <t>https://www.indeed.com/viewjob?jk=0d956b2a0c9bb45a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Consultant, Cloud Solutions</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Burwood Group</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=411c82ee69f9645d</t>
+          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9661a8215828cb59</t>
+          <t>https://www.indeed.com/viewjob?jk=d73094e1a0a14b40</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
+          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Intellirent</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Roanoke, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
+          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d956b2a0c9bb45a</t>
+          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Consultant, Cloud Solutions</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Burwood Group</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
+          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d73094e1a0a14b40</t>
+          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Stelo Support Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>STELO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
+          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Stelo Support Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>STELO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Principle Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Blob Storage, Dataflow, Scala, SQL Server, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
+          <t>https://www.indeed.com/viewjob?jk=e26a94c5a6adceae</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Data Specialist</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>via</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, Azure, PostgreSQL, ETL, ELT, dbt, pytest, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=bc8c37d3b685ec0e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Machine Learning</t>
+          <t>Data Integration Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Austin Community College</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, NoSQL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f160aadc0d3bdd6</t>
+          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
         </is>
       </c>
     </row>
@@ -3402,251 +3402,6 @@
       <c r="G85" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2d5d88d53c2ff675</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Databricks Architect</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Onebridge</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Principle Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Paradigm</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Virginia Beach, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Blob Storage, Dataflow, Scala, SQL Server, CI/CD, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e26a94c5a6adceae</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Stelo Support Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>STELO</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Stelo Support Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>STELO</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Data Specialist</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>via</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Somerville, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, Azure, PostgreSQL, ETL, ELT, dbt, pytest, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8c37d3b685ec0e</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Data Integration Developer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Austin Community College</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Intuitive (Intuitive Surgical)</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Peachtree Corners, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes, Git, Bitbucket</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3677cf32b1561e4d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-16.xlsx
+++ b/results/job_matches_2026-05-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,7 +543,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Exponent Technology Trading company DWC LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Applications Developer</t>
+          <t>AI Software Engineer III- PySpark, Python, AWS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Blob Storage, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40cf2df7dd84b43b</t>
+          <t>https://www.indeed.com/viewjob?jk=222754f51ea12be7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Applications Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Medallion Architecture, Hadoop, Hive, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Blob Storage, Oracle, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=430b7dc361a7ba29</t>
+          <t>https://www.indeed.com/viewjob?jk=40cf2df7dd84b43b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Advanced Cloud Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Medallion Architecture, Hadoop, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77fa4bb580f7b02</t>
+          <t>https://www.indeed.com/viewjob?jk=430b7dc361a7ba29</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FullStack AWS AI Engineer</t>
+          <t>Senior Platform, DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe20ccdbad190f18</t>
+          <t>https://www.indeed.com/viewjob?jk=10b5742d09907dfe</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
+          <t>Sr Advanced Cloud Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44dd55cd74d57902</t>
+          <t>https://www.indeed.com/viewjob?jk=b77fa4bb580f7b02</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
+          <t>FullStack AWS AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b73c3206a7c35a</t>
+          <t>https://www.indeed.com/viewjob?jk=fe20ccdbad190f18</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd51f4466b978623</t>
+          <t>https://www.indeed.com/viewjob?jk=44dd55cd74d57902</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Data Engineer</t>
+          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Trade Desk</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbbb1cacaaeb3af</t>
+          <t>https://www.indeed.com/viewjob?jk=07b73c3206a7c35a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Data Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Trade Desk</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c3dda8a9a898a72</t>
+          <t>https://www.indeed.com/viewjob?jk=fd51f4466b978623</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Infrastructure Engineer (Terraform / IaC)</t>
+          <t>Senior Software Engineer-Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>The Trade Desk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff5ff5e83aa53c1</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbbb1cacaaeb3af</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer 2 ( Backend)</t>
+          <t>Senior Software Engineer-Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>The Trade Desk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
+          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=020cd3f89e269314</t>
+          <t>https://www.indeed.com/viewjob?jk=8c3dda8a9a898a72</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer 2 ( Backend)</t>
+          <t>Senior AWS Cloud Infrastructure Engineer (Terraform / IaC)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd22044f3d0a4060</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff5ff5e83aa53c1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer 2 ( Backend)</t>
+          <t>Software Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Fluency</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e3095eee752df8</t>
+          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior DevOps &amp; Site Reliability Engineer - Americas</t>
+          <t>Software Engineer 2 ( Backend)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Appspace</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be33dcc3ef2e6cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=020cd3f89e269314</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Databricks Architect | US</t>
+          <t>Software Engineer 2 ( Backend)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cuesta Partners</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a549584a5dbc708e</t>
+          <t>https://www.indeed.com/viewjob?jk=bd22044f3d0a4060</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer 2 ( Backend)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Biamp Systems</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619b21a83c2def71</t>
+          <t>https://www.indeed.com/viewjob?jk=54e3095eee752df8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Platform</t>
+          <t>Senior DevOps &amp; Site Reliability Engineer - Americas</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fluency</t>
+          <t>Appspace</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
+          <t>https://www.indeed.com/viewjob?jk=be33dcc3ef2e6cb9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Fort Meyers</t>
+          <t>Databricks Architect | US</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Cuesta Partners</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fort Myers, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f61b1f4473db23</t>
+          <t>https://www.indeed.com/viewjob?jk=a549584a5dbc708e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Biamp Systems</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, IAM, Azure, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cb79ea92c31c11</t>
+          <t>https://www.indeed.com/viewjob?jk=619b21a83c2def71</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Site AI Engineer - Fort Meyers</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Fort Myers, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15643afd51a012f</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f61b1f4473db23</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Infrastructure Engineer</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e7d086f3b943f3</t>
+          <t>https://www.indeed.com/viewjob?jk=96cb79ea92c31c11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Infrastructure Engineer</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f717e7ca607998f2</t>
+          <t>https://www.indeed.com/viewjob?jk=f15643afd51a012f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Adhesives Research</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Glen Rock, PA, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5351eb2f4c376213</t>
+          <t>https://www.indeed.com/viewjob?jk=526c7ffc59edd892</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Southern Trust Insurance Company</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Macon, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b659efacce143d</t>
+          <t>https://www.indeed.com/viewjob?jk=52e7d086f3b943f3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
+          <t>https://www.indeed.com/viewjob?jk=f717e7ca607998f2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Architect and Database Engineer (Hands on)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Stratus</t>
+          <t>Adhesives Research</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Glen Rock, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Hive, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927d413c04d6f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=5351eb2f4c376213</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c55dd3f9232ba677</t>
+          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,59 +1686,59 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6dc8c3a5470cf</t>
+          <t>https://www.indeed.com/viewjob?jk=3de44fa63b4b67d2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Architect and Database Engineer (Hands on)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Stratus</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Hive, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe2438fb1b9d07</t>
+          <t>https://www.indeed.com/viewjob?jk=927d413c04d6f9fa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Engineer II, Cloud &amp; Web Systems Software</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Masimo</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=c55dd3f9232ba677</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b576f637ff969834</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd6dc8c3a5470cf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179695ff545f1e20</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Camas, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41e7b2135c1ebf09</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d929fe14c4afbac2</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe2438fb1b9d07</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Engineer II, Cloud &amp; Web Systems Software</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Masimo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca030c7965ce41e</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afcb01b26889c52</t>
+          <t>https://www.indeed.com/viewjob?jk=b576f637ff969834</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed2747917ef629b6</t>
+          <t>https://www.indeed.com/viewjob?jk=179695ff545f1e20</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>S3, RDS, Kafka, Snowflake, Time Travel, clustering keys, ETL, ELT, Tableau, Tableau Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df16bce6ff0b45b9</t>
+          <t>https://www.indeed.com/viewjob?jk=41e7b2135c1ebf09</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer – Remote / Flexible</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sparklebulb</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=d929fe14c4afbac2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Verkada</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
+          <t>https://www.indeed.com/viewjob?jk=dca030c7965ce41e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Software</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
+          <t>https://www.indeed.com/viewjob?jk=5afcb01b26889c52</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Allworth Financial</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,14 +2176,14 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d2bdc3bf9a8a45</t>
+          <t>https://www.indeed.com/viewjob?jk=ed2747917ef629b6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2193,15 +2193,15 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>S3, RDS, Kafka, Snowflake, Time Travel, clustering keys, ETL, ELT, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd6d6bd7fa1196f</t>
+          <t>https://www.indeed.com/viewjob?jk=df16bce6ff0b45b9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SAP NS2 DevOps Engineer</t>
+          <t>Data Engineer – Remote / Flexible</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Sparklebulb</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e077c2e8ed4afda</t>
+          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Automation Developer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Yale New Haven Health</t>
+          <t>Verkada</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Stratford, CT, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f343549fb0b598c9</t>
+          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Analyst - GPSC</t>
+          <t>Senior Data Engineer - Software</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
+          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Software Developer (Data Agents)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Allworth Financial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
+          <t>https://www.indeed.com/viewjob?jk=23d2bdc3bf9a8a45</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,182 +2376,182 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd6d6bd7fa1196f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SAP NS2 DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
+          <t>https://www.indeed.com/viewjob?jk=1e077c2e8ed4afda</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Automation Developer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Yale New Haven Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Stratford, CT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
+          <t>https://www.indeed.com/viewjob?jk=f343549fb0b598c9</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Business Intelligence Data Analyst - GPSC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>Sr Software Developer (Data Agents)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,59 +2561,59 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
+          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
+          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer (AWS/Call Center)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RealTruck</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eacf8e440d50fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Technical Product Owner II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Computer Services Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,112 +2656,112 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Snowflake, Oracle, Data Modeling, ELT, dbt, Power BI, Tableau</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=844a388f6929d4ff</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Scientist + Machine Learning Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NEOTAX</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4f8692b1b780d5</t>
+          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b00c104b625fb</t>
+          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=411c82ee69f9645d</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Sr. Platform Engineer (AWS/Call Center)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>RealTruck</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9661a8215828cb59</t>
+          <t>https://www.indeed.com/viewjob?jk=5eacf8e440d50fc0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Technical Product Owner II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Computer Services Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2862,38 +2862,38 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>RDS, Azure, Spark, Snowflake, Oracle, Data Modeling, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
+          <t>https://www.indeed.com/viewjob?jk=844a388f6929d4ff</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
+          <t>Senior Data Scientist + Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Intellirent</t>
+          <t>NEOTAX</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Roanoke, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
+          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d956b2a0c9bb45a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4f8692b1b780d5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Consultant, Cloud Solutions</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Burwood Group</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b00c104b625fb</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d73094e1a0a14b40</t>
+          <t>https://www.indeed.com/viewjob?jk=411c82ee69f9645d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,29 +3041,29 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
+          <t>https://www.indeed.com/viewjob?jk=9661a8215828cb59</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Onebridge</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
+          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Intellirent</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Roanoke, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Consultant, Cloud Solutions</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Burwood Group</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
+          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
+          <t>https://www.indeed.com/viewjob?jk=d73094e1a0a14b40</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Stelo Support Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>STELO</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
+          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Stelo Support Engineer</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>STELO</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
+          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
         </is>
       </c>
     </row>
@@ -3303,17 +3303,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Specialist</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>via</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, PostgreSQL, ETL, ELT, dbt, pytest, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8c37d3b685ec0e</t>
+          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Integration Developer</t>
+          <t>Data Specialist</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Austin Community College</t>
+          <t>via</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Azure, PostgreSQL, ETL, ELT, dbt, pytest, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=bc8c37d3b685ec0e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
+          <t>Data Integration Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Paramount Streaming</t>
+          <t>Austin Community College</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,15 +3391,190 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Edward Jones</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Edward Jones</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Stelo Support Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>STELO</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Stelo Support Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>STELO</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Paramount Streaming</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2d5d88d53c2ff675</t>
         </is>

--- a/results/job_matches_2026-05-16.xlsx
+++ b/results/job_matches_2026-05-16.xlsx
@@ -3268,17 +3268,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Principle Infrastructure Engineer</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Paradigm</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Dataflow, Scala, SQL Server, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26a94c5a6adceae</t>
+          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Principle Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Onebridge</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
+          <t>RDS, Azure, Blob Storage, Dataflow, Scala, SQL Server, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
+          <t>https://www.indeed.com/viewjob?jk=e26a94c5a6adceae</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-16.xlsx
+++ b/results/job_matches_2026-05-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Software Engineer III- PySpark, Python, AWS</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Medallion Architecture, Hadoop, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222754f51ea12be7</t>
+          <t>https://www.indeed.com/viewjob?jk=430b7dc361a7ba29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Applications Developer</t>
+          <t>AI Software Engineer III- PySpark, Python, AWS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Blob Storage, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40cf2df7dd84b43b</t>
+          <t>https://www.indeed.com/viewjob?jk=222754f51ea12be7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Applications Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Medallion Architecture, Hadoop, Hive, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Blob Storage, Oracle, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=430b7dc361a7ba29</t>
+          <t>https://www.indeed.com/viewjob?jk=40cf2df7dd84b43b</t>
         </is>
       </c>
     </row>
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c55dd3f9232ba677</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Camas, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6dc8c3a5470cf</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=c55dd3f9232ba677</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Camas, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe2438fb1b9d07</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe2438fb1b9d07</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd6dc8c3a5470cf</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer – Remote / Flexible</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sparklebulb</t>
+          <t>Verkada</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Software</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Verkada</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
+          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Software</t>
+          <t>Data Engineer – Remote / Flexible</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Sparklebulb</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
+          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SAP NS2 DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e077c2e8ed4afda</t>
+          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Automation Developer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Yale New Haven Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Stratford, CT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
+          <t>https://www.indeed.com/viewjob?jk=f343549fb0b598c9</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Automation Developer II</t>
+          <t>Business Intelligence Data Analyst - GPSC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Yale New Haven Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Stratford, CT, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f343549fb0b598c9</t>
+          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Analyst - GPSC</t>
+          <t>Sr Software Developer (Data Agents)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
+          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Software Developer (Data Agents)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,52 +2551,52 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
+          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
+          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
+          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Sr. Platform Engineer (AWS/Call Center)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>RealTruck</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
+          <t>https://www.indeed.com/viewjob?jk=5eacf8e440d50fc0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer (AWS/Call Center)</t>
+          <t>Technical Product Owner II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RealTruck</t>
+          <t>Computer Services Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Spark, Snowflake, Oracle, Data Modeling, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eacf8e440d50fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=844a388f6929d4ff</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Technical Product Owner II</t>
+          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Computer Services Inc.</t>
+          <t>Intellirent</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Roanoke, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Snowflake, Oracle, Data Modeling, ELT, dbt, Power BI, Tableau</t>
+          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=844a388f6929d4ff</t>
+          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Scientist + Machine Learning Engineer</t>
+          <t>Consultant, Cloud Solutions</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NEOTAX</t>
+          <t>Burwood Group</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
+          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4f8692b1b780d5</t>
+          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Senior Data Scientist + Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>NEOTAX</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b00c104b625fb</t>
+          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=411c82ee69f9645d</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4f8692b1b780d5</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9661a8215828cb59</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b00c104b625fb</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3081,29 +3081,29 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
+          <t>https://www.indeed.com/viewjob?jk=411c82ee69f9645d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Intellirent</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Roanoke, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
+          <t>https://www.indeed.com/viewjob?jk=9661a8215828cb59</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Consultant, Cloud Solutions</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Burwood Group</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
+          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d73094e1a0a14b40</t>
+          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
+          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Principle Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>RDS, Azure, Blob Storage, Dataflow, Scala, SQL Server, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=e26a94c5a6adceae</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Data Specialist</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Onebridge</t>
+          <t>via</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
+          <t>AWS, Azure, PostgreSQL, ETL, ELT, dbt, pytest, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
+          <t>https://www.indeed.com/viewjob?jk=bc8c37d3b685ec0e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Principle Infrastructure Engineer</t>
+          <t>Data Integration Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Paradigm</t>
+          <t>Austin Community College</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Dataflow, Scala, SQL Server, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26a94c5a6adceae</t>
+          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Specialist</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>via</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, PostgreSQL, ETL, ELT, dbt, pytest, Airflow, Git, Python</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8c37d3b685ec0e</t>
+          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Integration Developer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Austin Community College</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Stelo Support Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>STELO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
+          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Stelo Support Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>STELO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,19 +3471,19 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Stelo Support Engineer</t>
+          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>STELO</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3505,76 +3505,6 @@
         </is>
       </c>
       <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Stelo Support Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>STELO</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Paramount Streaming</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2d5d88d53c2ff675</t>
         </is>

--- a/results/job_matches_2026-05-16.xlsx
+++ b/results/job_matches_2026-05-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Software Engineer III- PySpark, Python, AWS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Medallion Architecture, Hadoop, Hive, Spark, PySpark</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=430b7dc361a7ba29</t>
+          <t>https://www.indeed.com/viewjob?jk=222754f51ea12be7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Software Engineer III- PySpark, Python, AWS</t>
+          <t>Senior Applications Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Blob Storage, Oracle, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222754f51ea12be7</t>
+          <t>https://www.indeed.com/viewjob?jk=40cf2df7dd84b43b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Applications Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Blob Storage, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Medallion Architecture, Hadoop, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40cf2df7dd84b43b</t>
+          <t>https://www.indeed.com/viewjob?jk=430b7dc361a7ba29</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Platform</t>
+          <t>Microsoft Fabric Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fluency</t>
+          <t>Troutman Pepper Locke</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
+          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer 2 ( Backend)</t>
+          <t>Software Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Fluency</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=020cd3f89e269314</t>
+          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd22044f3d0a4060</t>
+          <t>https://www.indeed.com/viewjob?jk=020cd3f89e269314</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e3095eee752df8</t>
+          <t>https://www.indeed.com/viewjob?jk=bd22044f3d0a4060</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevOps &amp; Site Reliability Engineer - Americas</t>
+          <t>Software Engineer 2 ( Backend)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Appspace</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be33dcc3ef2e6cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=54e3095eee752df8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Databricks Architect | US</t>
+          <t>Senior DevOps &amp; Site Reliability Engineer - Americas</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cuesta Partners</t>
+          <t>Appspace</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a549584a5dbc708e</t>
+          <t>https://www.indeed.com/viewjob?jk=be33dcc3ef2e6cb9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Databricks Architect | US</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Biamp Systems</t>
+          <t>Cuesta Partners</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619b21a83c2def71</t>
+          <t>https://www.indeed.com/viewjob?jk=a549584a5dbc708e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Fort Meyers</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Biamp Systems</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fort Myers, FL, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, IAM, Azure, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f61b1f4473db23</t>
+          <t>https://www.indeed.com/viewjob?jk=619b21a83c2def71</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Site AI Engineer - Fort Meyers</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Fort Myers, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cb79ea92c31c11</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f61b1f4473db23</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15643afd51a012f</t>
+          <t>https://www.indeed.com/viewjob?jk=96cb79ea92c31c11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526c7ffc59edd892</t>
+          <t>https://www.indeed.com/viewjob?jk=f15643afd51a012f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Infrastructure Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e7d086f3b943f3</t>
+          <t>https://www.indeed.com/viewjob?jk=526c7ffc59edd892</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f717e7ca607998f2</t>
+          <t>https://www.indeed.com/viewjob?jk=52e7d086f3b943f3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Adhesives Research</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Glen Rock, PA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5351eb2f4c376213</t>
+          <t>https://www.indeed.com/viewjob?jk=f717e7ca607998f2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Adhesives Research</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Glen Rock, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
+          <t>https://www.indeed.com/viewjob?jk=5351eb2f4c376213</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de44fa63b4b67d2</t>
+          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Architect and Database Engineer (Hands on)</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Stratus</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Hive, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927d413c04d6f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=3de44fa63b4b67d2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect and Database Engineer (Hands on)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>Stratus</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Hive, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=927d413c04d6f9fa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Camas, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=c55dd3f9232ba677</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c55dd3f9232ba677</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Camas, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe2438fb1b9d07</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6dc8c3a5470cf</t>
+          <t>https://www.indeed.com/viewjob?jk=64fe2438fb1b9d07</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer – Remote / Flexible</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Verkada</t>
+          <t>Sparklebulb</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
+          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
+          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Verkada</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
+          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer – Remote / Flexible</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sparklebulb</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=63c010146ae6d1df</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer - Software</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Allworth Financial</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d2bdc3bf9a8a45</t>
+          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Allworth Financial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd6d6bd7fa1196f</t>
+          <t>https://www.indeed.com/viewjob?jk=23d2bdc3bf9a8a45</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd6d6bd7fa1196f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Automation Developer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Yale New Haven Health</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Stratford, CT, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f343549fb0b598c9</t>
+          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Analyst - GPSC</t>
+          <t>AI Automation Developer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Yale New Haven Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Stratford, CT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
+          <t>https://www.indeed.com/viewjob?jk=f343549fb0b598c9</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Software Developer (Data Agents)</t>
+          <t>Business Intelligence Data Analyst - GPSC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
+          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Developer (Data Agents)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,52 +2551,52 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
+          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
+          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
+          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer (AWS/Call Center)</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RealTruck</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eacf8e440d50fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Technical Product Owner II</t>
+          <t>Sr. Platform Engineer (AWS/Call Center)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Computer Services Inc.</t>
+          <t>RealTruck</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Snowflake, Oracle, Data Modeling, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=844a388f6929d4ff</t>
+          <t>https://www.indeed.com/viewjob?jk=5eacf8e440d50fc0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
+          <t>Technical Product Owner II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Intellirent</t>
+          <t>Computer Services Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Roanoke, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
+          <t>RDS, Azure, Spark, Snowflake, Oracle, Data Modeling, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
+          <t>https://www.indeed.com/viewjob?jk=844a388f6929d4ff</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Consultant, Cloud Solutions</t>
+          <t>Senior Data Scientist + Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Burwood Group</t>
+          <t>NEOTAX</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
+          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4f8692b1b780d5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Scientist + Machine Learning Engineer</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NEOTAX</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b00c104b625fb</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4f8692b1b780d5</t>
+          <t>https://www.indeed.com/viewjob?jk=411c82ee69f9645d</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b00c104b625fb</t>
+          <t>https://www.indeed.com/viewjob?jk=9661a8215828cb59</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3081,29 +3081,29 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=411c82ee69f9645d</t>
+          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Data Engineer (Contract-to-Hire, Part-Time)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>ZENO Group</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9661a8215828cb59</t>
+          <t>https://www.indeed.com/viewjob?jk=15ed8a390361bf1a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Intellirent</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Roanoke, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
+          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Consultant, Cloud Solutions</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Burwood Group</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Onebridge</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
+          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Principle Infrastructure Engineer</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Paradigm</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Dataflow, Scala, SQL Server, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26a94c5a6adceae</t>
+          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Specialist</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>via</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, PostgreSQL, ETL, ELT, dbt, pytest, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8c37d3b685ec0e</t>
+          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Integration Developer</t>
+          <t>Principle Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Austin Community College</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Blob Storage, Dataflow, Scala, SQL Server, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=e26a94c5a6adceae</t>
         </is>
       </c>
     </row>
@@ -3478,17 +3478,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
+          <t>Data Specialist</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Paramount Streaming</t>
+          <t>via</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,15 +3496,85 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>AWS, Azure, PostgreSQL, ETL, ELT, dbt, pytest, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc8c37d3b685ec0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Data Integration Developer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Austin Community College</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Paramount Streaming</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2d5d88d53c2ff675</t>
         </is>

--- a/results/job_matches_2026-05-16.xlsx
+++ b/results/job_matches_2026-05-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Platform, DevOps Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b5742d09907dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=62ca3c3ce12832cd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Advanced Cloud Developer</t>
+          <t>Senior Platform, DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77fa4bb580f7b02</t>
+          <t>https://www.indeed.com/viewjob?jk=10b5742d09907dfe</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FullStack AWS AI Engineer</t>
+          <t>Sr Advanced Cloud Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe20ccdbad190f18</t>
+          <t>https://www.indeed.com/viewjob?jk=b77fa4bb580f7b02</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
+          <t>FullStack AWS AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44dd55cd74d57902</t>
+          <t>https://www.indeed.com/viewjob?jk=fe20ccdbad190f18</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b73c3206a7c35a</t>
+          <t>https://www.indeed.com/viewjob?jk=44dd55cd74d57902</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd51f4466b978623</t>
+          <t>https://www.indeed.com/viewjob?jk=07b73c3206a7c35a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Data Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Trade Desk</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbbb1cacaaeb3af</t>
+          <t>https://www.indeed.com/viewjob?jk=fd51f4466b978623</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c3dda8a9a898a72</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbbb1cacaaeb3af</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Infrastructure Engineer (Terraform / IaC)</t>
+          <t>Senior Software Engineer-Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>The Trade Desk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff5ff5e83aa53c1</t>
+          <t>https://www.indeed.com/viewjob?jk=8c3dda8a9a898a72</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Architect</t>
+          <t>Senior AWS Cloud Infrastructure Engineer (Terraform / IaC)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Troutman Pepper Locke</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff5ff5e83aa53c1</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer 2 ( Backend)</t>
+          <t>Microsoft Fabric Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Troutman Pepper Locke</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=020cd3f89e269314</t>
+          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd22044f3d0a4060</t>
+          <t>https://www.indeed.com/viewjob?jk=020cd3f89e269314</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e3095eee752df8</t>
+          <t>https://www.indeed.com/viewjob?jk=bd22044f3d0a4060</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior DevOps &amp; Site Reliability Engineer - Americas</t>
+          <t>Software Engineer 2 ( Backend)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Appspace</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be33dcc3ef2e6cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=54e3095eee752df8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Databricks Architect | US</t>
+          <t>Senior DevOps &amp; Site Reliability Engineer - Americas</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cuesta Partners</t>
+          <t>Appspace</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a549584a5dbc708e</t>
+          <t>https://www.indeed.com/viewjob?jk=be33dcc3ef2e6cb9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Databricks Architect | US</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Biamp Systems</t>
+          <t>Cuesta Partners</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619b21a83c2def71</t>
+          <t>https://www.indeed.com/viewjob?jk=a549584a5dbc708e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Fort Meyers</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Biamp Systems</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fort Myers, FL, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, IAM, Azure, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f61b1f4473db23</t>
+          <t>https://www.indeed.com/viewjob?jk=619b21a83c2def71</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Site AI Engineer - Fort Meyers</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Fort Myers, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cb79ea92c31c11</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f61b1f4473db23</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15643afd51a012f</t>
+          <t>https://www.indeed.com/viewjob?jk=96cb79ea92c31c11</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526c7ffc59edd892</t>
+          <t>https://www.indeed.com/viewjob?jk=f15643afd51a012f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Infrastructure Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e7d086f3b943f3</t>
+          <t>https://www.indeed.com/viewjob?jk=526c7ffc59edd892</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f717e7ca607998f2</t>
+          <t>https://www.indeed.com/viewjob?jk=52e7d086f3b943f3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Adhesives Research</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Glen Rock, PA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5351eb2f4c376213</t>
+          <t>https://www.indeed.com/viewjob?jk=f717e7ca607998f2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Adhesives Research</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Glen Rock, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
+          <t>https://www.indeed.com/viewjob?jk=5351eb2f4c376213</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de44fa63b4b67d2</t>
+          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Architect and Database Engineer (Hands on)</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Stratus</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, GCP, Hive, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927d413c04d6f9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=3de44fa63b4b67d2</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II, Cloud &amp; Web Systems Software</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Masimo</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fe2438fb1b9d07</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Engineer II, Cloud &amp; Web Systems Software</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Masimo</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=b576f637ff969834</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b576f637ff969834</t>
+          <t>https://www.indeed.com/viewjob?jk=179695ff545f1e20</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179695ff545f1e20</t>
+          <t>https://www.indeed.com/viewjob?jk=41e7b2135c1ebf09</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41e7b2135c1ebf09</t>
+          <t>https://www.indeed.com/viewjob?jk=d929fe14c4afbac2</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d929fe14c4afbac2</t>
+          <t>https://www.indeed.com/viewjob?jk=dca030c7965ce41e</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca030c7965ce41e</t>
+          <t>https://www.indeed.com/viewjob?jk=5afcb01b26889c52</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afcb01b26889c52</t>
+          <t>https://www.indeed.com/viewjob?jk=ed2747917ef629b6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>S3, RDS, Kafka, Snowflake, Time Travel, clustering keys, ETL, ELT, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed2747917ef629b6</t>
+          <t>https://www.indeed.com/viewjob?jk=df16bce6ff0b45b9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Data Engineer – Remote / Flexible</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Sparklebulb</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>S3, RDS, Kafka, Snowflake, Time Travel, clustering keys, ETL, ELT, Tableau, Tableau Server</t>
+          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df16bce6ff0b45b9</t>
+          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer – Remote / Flexible</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sparklebulb</t>
+          <t>Verkada</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Verkada</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
+          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
+          <t>https://www.indeed.com/viewjob?jk=63c010146ae6d1df</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Senior Data Engineer - Software</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c010146ae6d1df</t>
+          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Software</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Allworth Financial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
+          <t>https://www.indeed.com/viewjob?jk=23d2bdc3bf9a8a45</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Allworth Financial</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d2bdc3bf9a8a45</t>
+          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>AI Automation Developer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Yale New Haven Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Stratford, CT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd6d6bd7fa1196f</t>
+          <t>https://www.indeed.com/viewjob?jk=f343549fb0b598c9</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence Data Analyst - GPSC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
+          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Automation Developer II</t>
+          <t>Sr Software Developer (Data Agents)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Yale New Haven Health</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Stratford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f343549fb0b598c9</t>
+          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Analyst - GPSC</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,87 +2516,87 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
+          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Software Developer (Data Agents)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
+          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
+          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
+          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>Sr. Platform Engineer (AWS/Call Center)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>RealTruck</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=5eacf8e440d50fc0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Technical Product Owner II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Computer Services Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Spark, Snowflake, Oracle, Data Modeling, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
+          <t>https://www.indeed.com/viewjob?jk=844a388f6929d4ff</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer (AWS/Call Center)</t>
+          <t>Senior Data Scientist + Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RealTruck</t>
+          <t>NEOTAX</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eacf8e440d50fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Technical Product Owner II</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Computer Services Inc.</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Snowflake, Oracle, Data Modeling, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=844a388f6929d4ff</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4f8692b1b780d5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Scientist + Machine Learning Engineer</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NEOTAX</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e99b00c104b625fb</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4f8692b1b780d5</t>
+          <t>https://www.indeed.com/viewjob?jk=411c82ee69f9645d</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b00c104b625fb</t>
+          <t>https://www.indeed.com/viewjob?jk=9661a8215828cb59</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3011,29 +3011,29 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=411c82ee69f9645d</t>
+          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Data Engineer (Contract-to-Hire, Part-Time)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>ZENO Group</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9661a8215828cb59</t>
+          <t>https://www.indeed.com/viewjob?jk=15ed8a390361bf1a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Intellirent</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Roanoke, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,29 +3076,29 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
+          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer (Contract-to-Hire, Part-Time)</t>
+          <t>Consultant, Cloud Solutions</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ZENO Group</t>
+          <t>Burwood Group</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ed8a390361bf1a</t>
+          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Intellirent</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Roanoke, TX, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
+          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Consultant, Cloud Solutions</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Burwood Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
+          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Principle Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Blob Storage, Dataflow, Scala, SQL Server, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
+          <t>https://www.indeed.com/viewjob?jk=e26a94c5a6adceae</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Onebridge</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
+          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Principle Infrastructure Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Paradigm</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Dataflow, Scala, SQL Server, CI/CD, Terraform, Git, Python</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26a94c5a6adceae</t>
+          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Stelo Support Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>STELO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
+          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Stelo Support Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>STELO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Stelo Support Engineer</t>
+          <t>Data Integration Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>STELO</t>
+          <t>Austin Community College</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
+          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Stelo Support Engineer</t>
+          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>STELO</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3470,111 +3470,6 @@
         </is>
       </c>
       <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Data Specialist</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>via</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Somerville, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, Azure, PostgreSQL, ETL, ELT, dbt, pytest, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8c37d3b685ec0e</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Data Integration Developer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Austin Community College</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Paramount Streaming</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2d5d88d53c2ff675</t>
         </is>

--- a/results/job_matches_2026-05-16.xlsx
+++ b/results/job_matches_2026-05-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Microsoft Azure Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>CSIK Consulting</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Medallion Architecture, Hadoop, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=430b7dc361a7ba29</t>
+          <t>https://www.indeed.com/viewjob?jk=fab3c4481b723cee</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Medallion Architecture, Hadoop, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62ca3c3ce12832cd</t>
+          <t>https://www.indeed.com/viewjob?jk=430b7dc361a7ba29</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Platform, DevOps Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b5742d09907dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=62ca3c3ce12832cd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Advanced Cloud Developer</t>
+          <t>Senior Platform, DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77fa4bb580f7b02</t>
+          <t>https://www.indeed.com/viewjob?jk=10b5742d09907dfe</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FullStack AWS AI Engineer</t>
+          <t>Sr Advanced Cloud Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe20ccdbad190f18</t>
+          <t>https://www.indeed.com/viewjob?jk=b77fa4bb580f7b02</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
+          <t>FullStack AWS AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44dd55cd74d57902</t>
+          <t>https://www.indeed.com/viewjob?jk=fe20ccdbad190f18</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b73c3206a7c35a</t>
+          <t>https://www.indeed.com/viewjob?jk=44dd55cd74d57902</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd51f4466b978623</t>
+          <t>https://www.indeed.com/viewjob?jk=07b73c3206a7c35a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Data Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Trade Desk</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbbb1cacaaeb3af</t>
+          <t>https://www.indeed.com/viewjob?jk=fd51f4466b978623</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c3dda8a9a898a72</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbbb1cacaaeb3af</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Infrastructure Engineer (Terraform / IaC)</t>
+          <t>Senior Software Engineer-Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>The Trade Desk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff5ff5e83aa53c1</t>
+          <t>https://www.indeed.com/viewjob?jk=8c3dda8a9a898a72</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Platform</t>
+          <t>Microsoft Fabric Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fluency</t>
+          <t>Troutman Pepper Locke</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
+          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Architect</t>
+          <t>Software Engineer 2 ( Backend)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Troutman Pepper Locke</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=020cd3f89e269314</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=020cd3f89e269314</t>
+          <t>https://www.indeed.com/viewjob?jk=bd22044f3d0a4060</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd22044f3d0a4060</t>
+          <t>https://www.indeed.com/viewjob?jk=54e3095eee752df8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer 2 ( Backend)</t>
+          <t>Senior DevOps &amp; Site Reliability Engineer - Americas</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Appspace</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e3095eee752df8</t>
+          <t>https://www.indeed.com/viewjob?jk=be33dcc3ef2e6cb9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps &amp; Site Reliability Engineer - Americas</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Appspace</t>
+          <t>Biamp Systems</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, Azure, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be33dcc3ef2e6cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=619b21a83c2def71</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Databricks Architect | US</t>
+          <t>Software Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cuesta Partners</t>
+          <t>Fluency</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a549584a5dbc708e</t>
+          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Site AI Engineer - Fort Meyers</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Biamp Systems</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Fort Myers, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619b21a83c2def71</t>
+          <t>https://www.indeed.com/viewjob?jk=b3f61b1f4473db23</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Fort Meyers</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fort Myers, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f61b1f4473db23</t>
+          <t>https://www.indeed.com/viewjob?jk=96cb79ea92c31c11</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cb79ea92c31c11</t>
+          <t>https://www.indeed.com/viewjob?jk=f15643afd51a012f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15643afd51a012f</t>
+          <t>https://www.indeed.com/viewjob?jk=526c7ffc59edd892</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526c7ffc59edd892</t>
+          <t>https://www.indeed.com/viewjob?jk=52e7d086f3b943f3</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e7d086f3b943f3</t>
+          <t>https://www.indeed.com/viewjob?jk=f717e7ca607998f2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Adhesives Research</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Glen Rock, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f717e7ca607998f2</t>
+          <t>https://www.indeed.com/viewjob?jk=5351eb2f4c376213</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Adhesives Research</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Glen Rock, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5351eb2f4c376213</t>
+          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,42 +1711,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
+          <t>https://www.indeed.com/viewjob?jk=3de44fa63b4b67d2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de44fa63b4b67d2</t>
+          <t>https://www.indeed.com/viewjob?jk=c55dd3f9232ba677</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c55dd3f9232ba677</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Camas, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II, Cloud &amp; Web Systems Software</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>Masimo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Camas, WA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Engineer II, Cloud &amp; Web Systems Software</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Masimo</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=b576f637ff969834</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b576f637ff969834</t>
+          <t>https://www.indeed.com/viewjob?jk=179695ff545f1e20</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179695ff545f1e20</t>
+          <t>https://www.indeed.com/viewjob?jk=41e7b2135c1ebf09</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41e7b2135c1ebf09</t>
+          <t>https://www.indeed.com/viewjob?jk=d929fe14c4afbac2</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d929fe14c4afbac2</t>
+          <t>https://www.indeed.com/viewjob?jk=dca030c7965ce41e</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca030c7965ce41e</t>
+          <t>https://www.indeed.com/viewjob?jk=5afcb01b26889c52</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afcb01b26889c52</t>
+          <t>https://www.indeed.com/viewjob?jk=ed2747917ef629b6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>S3, RDS, Kafka, Snowflake, Time Travel, clustering keys, ETL, ELT, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed2747917ef629b6</t>
+          <t>https://www.indeed.com/viewjob?jk=df16bce6ff0b45b9</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Data Engineer – Remote / Flexible</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Sparklebulb</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>S3, RDS, Kafka, Snowflake, Time Travel, clustering keys, ETL, ELT, Tableau, Tableau Server</t>
+          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df16bce6ff0b45b9</t>
+          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer – Remote / Flexible</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sparklebulb</t>
+          <t>Verkada</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Verkada</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
+          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
+          <t>https://www.indeed.com/viewjob?jk=63c010146ae6d1df</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Senior Data Engineer - Software</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c010146ae6d1df</t>
+          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Software</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Allworth Financial</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
+          <t>https://www.indeed.com/viewjob?jk=23d2bdc3bf9a8a45</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Allworth Financial</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d2bdc3bf9a8a45</t>
+          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Automation Developer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Yale New Haven Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Stratford, CT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
+          <t>https://www.indeed.com/viewjob?jk=f343549fb0b598c9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Automation Developer II</t>
+          <t>Business Intelligence Data Analyst - GPSC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Yale New Haven Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Stratford, CT, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f343549fb0b598c9</t>
+          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Analyst - GPSC</t>
+          <t>Sr Software Developer (Data Agents)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
+          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Software Developer (Data Agents)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,52 +2481,52 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
+          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
+          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
+          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Senior Data Scientist + Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>NEOTAX</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
+          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Platform Engineer (AWS/Call Center)</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RealTruck</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eacf8e440d50fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Technical Product Owner II</t>
+          <t>Data Engineer (Contract-to-Hire, Part-Time)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Computer Services Inc.</t>
+          <t>ZENO Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Snowflake, Oracle, Data Modeling, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=844a388f6929d4ff</t>
+          <t>https://www.indeed.com/viewjob?jk=15ed8a390361bf1a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Scientist + Machine Learning Engineer</t>
+          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NEOTAX</t>
+          <t>Intellirent</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Roanoke, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
+          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
+          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4f8692b1b780d5</t>
+          <t>https://www.indeed.com/viewjob?jk=0d956b2a0c9bb45a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99b00c104b625fb</t>
+          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=411c82ee69f9645d</t>
+          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9661a8215828cb59</t>
+          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Principle Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>RDS, Azure, Blob Storage, Dataflow, Scala, SQL Server, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
+          <t>https://www.indeed.com/viewjob?jk=e26a94c5a6adceae</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer (Contract-to-Hire, Part-Time)</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ZENO Group</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ed8a390361bf1a</t>
+          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Intellirent</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Roanoke, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
+          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Consultant, Cloud Solutions</t>
+          <t>Stelo Support Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Burwood Group</t>
+          <t>STELO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead15ecd3721fe70</t>
+          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Stelo Support Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>STELO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Data Integration Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Austin Community College</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Principle Infrastructure Engineer</t>
+          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Paradigm</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Dataflow, Scala, SQL Server, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3225,251 +3225,6 @@
         </is>
       </c>
       <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e26a94c5a6adceae</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Databricks Architect</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Onebridge</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Stelo Support Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>STELO</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Stelo Support Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>STELO</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Data Integration Developer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Austin Community College</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Paramount Streaming</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2d5d88d53c2ff675</t>
         </is>

--- a/results/job_matches_2026-05-16.xlsx
+++ b/results/job_matches_2026-05-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Platform Engineering</t>
+          <t>Senior DJI Dock 2 / Cloud API Integration Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IntegriChain</t>
+          <t>Exponent Technology Trading company DWC LLC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31.2</v>
+        <v>18.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Timestream, Step Functions, S3, IAM, RDS, Azure</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a2a75955286c43d</t>
+          <t>https://www.indeed.com/viewjob?jk=f4968d826aaf9e4d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer - Azure &amp; Microsoft Fabric Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PGW Auto Glass</t>
+          <t>Educology Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cranberry Township, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3d77615dc2cb49</t>
+          <t>https://www.indeed.com/viewjob?jk=ea52f552407f8b0e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior DJI Dock 2 / Cloud API Integration Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Exponent Technology Trading company DWC LLC</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4968d826aaf9e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=76df9b54cd60a601</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Educology Solutions</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala</t>
+          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea52f552407f8b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=5902e7f954c993c8</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76df9b54cd60a601</t>
+          <t>https://www.indeed.com/viewjob?jk=e578397657651918</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>AI Software Engineer III- PySpark, Python, AWS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5902e7f954c993c8</t>
+          <t>https://www.indeed.com/viewjob?jk=222754f51ea12be7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Applications Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Blob Storage, Oracle, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e578397657651918</t>
+          <t>https://www.indeed.com/viewjob?jk=40cf2df7dd84b43b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Software Engineer III- PySpark, Python, AWS</t>
+          <t>Microsoft Azure Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CSIK Consulting</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222754f51ea12be7</t>
+          <t>https://www.indeed.com/viewjob?jk=fab3c4481b723cee</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Applications Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Blob Storage, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Medallion Architecture, Hadoop, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40cf2df7dd84b43b</t>
+          <t>https://www.indeed.com/viewjob?jk=430b7dc361a7ba29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CSIK Consulting</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab3c4481b723cee</t>
+          <t>https://www.indeed.com/viewjob?jk=62ca3c3ce12832cd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Platform, DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Medallion Architecture, Hadoop, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=430b7dc361a7ba29</t>
+          <t>https://www.indeed.com/viewjob?jk=10b5742d09907dfe</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Sr Advanced Cloud Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62ca3c3ce12832cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b77fa4bb580f7b02</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Platform, DevOps Engineer</t>
+          <t>FullStack AWS AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b5742d09907dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=fe20ccdbad190f18</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Advanced Cloud Developer</t>
+          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77fa4bb580f7b02</t>
+          <t>https://www.indeed.com/viewjob?jk=44dd55cd74d57902</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FullStack AWS AI Engineer</t>
+          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe20ccdbad190f18</t>
+          <t>https://www.indeed.com/viewjob?jk=07b73c3206a7c35a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44dd55cd74d57902</t>
+          <t>https://www.indeed.com/viewjob?jk=fd51f4466b978623</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
+          <t>Senior Software Engineer-Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>The Trade Desk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
+          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b73c3206a7c35a</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbbb1cacaaeb3af</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Senior Software Engineer-Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>The Trade Desk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, CI/CD</t>
+          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd51f4466b978623</t>
+          <t>https://www.indeed.com/viewjob?jk=8c3dda8a9a898a72</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Data Engineer</t>
+          <t>Microsoft Fabric Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Trade Desk</t>
+          <t>Troutman Pepper Locke</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbbb1cacaaeb3af</t>
+          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Data Engineer</t>
+          <t>Software Engineer 2 ( Backend)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Trade Desk</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c3dda8a9a898a72</t>
+          <t>https://www.indeed.com/viewjob?jk=020cd3f89e269314</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Architect</t>
+          <t>Software Engineer 2 ( Backend)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Troutman Pepper Locke</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=bd22044f3d0a4060</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=020cd3f89e269314</t>
+          <t>https://www.indeed.com/viewjob?jk=54e3095eee752df8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer 2 ( Backend)</t>
+          <t>Senior DevOps &amp; Site Reliability Engineer - Americas</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Appspace</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd22044f3d0a4060</t>
+          <t>https://www.indeed.com/viewjob?jk=be33dcc3ef2e6cb9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer 2 ( Backend)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Biamp Systems</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
+          <t>AWS, IAM, Azure, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e3095eee752df8</t>
+          <t>https://www.indeed.com/viewjob?jk=619b21a83c2def71</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior DevOps &amp; Site Reliability Engineer - Americas</t>
+          <t>Software Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Appspace</t>
+          <t>Fluency</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be33dcc3ef2e6cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Biamp Systems</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619b21a83c2def71</t>
+          <t>https://www.indeed.com/viewjob?jk=96cb79ea92c31c11</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Platform</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fluency</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
+          <t>https://www.indeed.com/viewjob?jk=f15643afd51a012f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Site AI Engineer - Fort Meyers</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fort Myers, FL, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3f61b1f4473db23</t>
+          <t>https://www.indeed.com/viewjob?jk=526c7ffc59edd892</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Senior Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cb79ea92c31c11</t>
+          <t>https://www.indeed.com/viewjob?jk=52e7d086f3b943f3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Senior Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15643afd51a012f</t>
+          <t>https://www.indeed.com/viewjob?jk=f717e7ca607998f2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Adhesives Research</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Glen Rock, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526c7ffc59edd892</t>
+          <t>https://www.indeed.com/viewjob?jk=5351eb2f4c376213</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Infrastructure Engineer</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e7d086f3b943f3</t>
+          <t>https://www.indeed.com/viewjob?jk=3de44fa63b4b67d2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Infrastructure Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f717e7ca607998f2</t>
+          <t>https://www.indeed.com/viewjob?jk=c55dd3f9232ba677</t>
         </is>
       </c>
     </row>
@@ -1628,20 +1628,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Adhesives Research</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Glen Rock, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5351eb2f4c376213</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Camas, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b9f771df1c702a</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Engineer II, Cloud &amp; Web Systems Software</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Masimo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de44fa63b4b67d2</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>S3, RDS, Kafka, Snowflake, Time Travel, clustering keys, ETL, ELT, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c55dd3f9232ba677</t>
+          <t>https://www.indeed.com/viewjob?jk=df16bce6ff0b45b9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer – Remote / Flexible</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>Sparklebulb</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>Verkada</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Camas, WA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Engineer II, Cloud &amp; Web Systems Software</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Masimo</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=63c010146ae6d1df</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior Data Engineer - Software</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b576f637ff969834</t>
+          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Allworth Financial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179695ff545f1e20</t>
+          <t>https://www.indeed.com/viewjob?jk=23d2bdc3bf9a8a45</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41e7b2135c1ebf09</t>
+          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Business Intelligence Data Analyst - GPSC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d929fe14c4afbac2</t>
+          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Sr Software Developer (Data Agents)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,172 +2036,172 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca030c7965ce41e</t>
+          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5afcb01b26889c52</t>
+          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed2747917ef629b6</t>
+          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>S3, RDS, Kafka, Snowflake, Time Travel, clustering keys, ETL, ELT, Tableau, Tableau Server</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df16bce6ff0b45b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer – Remote / Flexible</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sparklebulb</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Verkada</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
+          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c010146ae6d1df</t>
+          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Software</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Scientist + Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Allworth Financial</t>
+          <t>NEOTAX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d2bdc3bf9a8a45</t>
+          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer (L2) Segment Team</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
+          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Automation Developer II</t>
+          <t>Data Engineer (Contract-to-Hire, Part-Time)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Yale New Haven Health</t>
+          <t>ZENO Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Stratford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, EMR, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f343549fb0b598c9</t>
+          <t>https://www.indeed.com/viewjob?jk=15ed8a390361bf1a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Analyst - GPSC</t>
+          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Intellirent</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Roanoke, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
+          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Software Developer (Data Agents)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,102 +2456,102 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
+          <t>https://www.indeed.com/viewjob?jk=0d956b2a0c9bb45a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
+          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
+          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,102 +2561,102 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Principle Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Blob Storage, Dataflow, Scala, SQL Server, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
+          <t>https://www.indeed.com/viewjob?jk=e26a94c5a6adceae</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Stelo Support Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>STELO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
+          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Scientist + Machine Learning Engineer</t>
+          <t>Stelo Support Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NEOTAX</t>
+          <t>STELO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Data Integration Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Austin Community College</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
+          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer (Contract-to-Hire, Part-Time)</t>
+          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ZENO Group</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2805,426 +2805,6 @@
         </is>
       </c>
       <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15ed8a390361bf1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Intellirent</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Roanoke, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Montefiore Einstein</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Yonkers, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d956b2a0c9bb45a</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Mission Pet Health</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>AL, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Databricks Architect</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Onebridge</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Claims Data Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Principle Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Paradigm</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Virginia Beach, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Blob Storage, Dataflow, Scala, SQL Server, CI/CD, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e26a94c5a6adceae</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Stelo Support Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>STELO</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Stelo Support Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>STELO</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Data Integration Developer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Austin Community College</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Paramount Streaming</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2d5d88d53c2ff675</t>
         </is>

--- a/results/job_matches_2026-05-16.xlsx
+++ b/results/job_matches_2026-05-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior DJI Dock 2 / Cloud API Integration Engineer</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Exponent Technology Trading company DWC LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,102 +496,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4968d826aaf9e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=cfeff295f2019956</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DJI Dock 2 / Cloud API Integration Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Educology Solutions</t>
+          <t>Exponent Technology Trading company DWC LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea52f552407f8b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=f4968d826aaf9e4d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76df9b54cd60a601</t>
+          <t>https://www.indeed.com/viewjob?jk=1def15e5de2b7c64</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Educology Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5902e7f954c993c8</t>
+          <t>https://www.indeed.com/viewjob?jk=ea52f552407f8b0e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>AI Software Engineer III- PySpark, Python, AWS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Azure, Databricks, Cloud Storage, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e578397657651918</t>
+          <t>https://www.indeed.com/viewjob?jk=222754f51ea12be7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Software Engineer III- PySpark, Python, AWS</t>
+          <t>Microsoft Azure Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CSIK Consulting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222754f51ea12be7</t>
+          <t>https://www.indeed.com/viewjob?jk=fab3c4481b723cee</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Applications Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Blob Storage, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Medallion Architecture, Hadoop, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40cf2df7dd84b43b</t>
+          <t>https://www.indeed.com/viewjob?jk=430b7dc361a7ba29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CSIK Consulting</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab3c4481b723cee</t>
+          <t>https://www.indeed.com/viewjob?jk=62ca3c3ce12832cd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Platform, DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Medallion Architecture, Hadoop, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,77 +776,77 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=430b7dc361a7ba29</t>
+          <t>https://www.indeed.com/viewjob?jk=10b5742d09907dfe</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62ca3c3ce12832cd</t>
+          <t>https://www.indeed.com/viewjob?jk=966e325f5ac56bee</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Platform, DevOps Engineer</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b5742d09907dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=64a90374f14eb8a5</t>
         </is>
       </c>
     </row>
@@ -923,60 +923,60 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44dd55cd74d57902</t>
+          <t>https://www.indeed.com/viewjob?jk=248664e537c28c4d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b73c3206a7c35a</t>
+          <t>https://www.indeed.com/viewjob?jk=fd51f4466b978623</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Senior Software Engineer-Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>The Trade Desk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, CI/CD</t>
+          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd51f4466b978623</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbbb1cacaaeb3af</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbbb1cacaaeb3af</t>
+          <t>https://www.indeed.com/viewjob?jk=8c3dda8a9a898a72</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Data Engineer</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Trade Desk</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c3dda8a9a898a72</t>
+          <t>https://www.indeed.com/viewjob?jk=35842df306ee4c2e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Architect</t>
+          <t>Software Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Troutman Pepper Locke</t>
+          <t>Fluency</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer 2 ( Backend)</t>
+          <t>Microsoft Fabric Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Troutman Pepper Locke</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=020cd3f89e269314</t>
+          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd22044f3d0a4060</t>
+          <t>https://www.indeed.com/viewjob?jk=020cd3f89e269314</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e3095eee752df8</t>
+          <t>https://www.indeed.com/viewjob?jk=bd22044f3d0a4060</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior DevOps &amp; Site Reliability Engineer - Americas</t>
+          <t>Software Engineer 2 ( Backend)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Appspace</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be33dcc3ef2e6cb9</t>
+          <t>https://www.indeed.com/viewjob?jk=54e3095eee752df8</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Platform</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fluency</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
+          <t>https://www.indeed.com/viewjob?jk=96cb79ea92c31c11</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cb79ea92c31c11</t>
+          <t>https://www.indeed.com/viewjob?jk=f15643afd51a012f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15643afd51a012f</t>
+          <t>https://www.indeed.com/viewjob?jk=526c7ffc59edd892</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526c7ffc59edd892</t>
+          <t>https://www.indeed.com/viewjob?jk=52e7d086f3b943f3</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e7d086f3b943f3</t>
+          <t>https://www.indeed.com/viewjob?jk=f717e7ca607998f2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Adhesives Research</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Glen Rock, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f717e7ca607998f2</t>
+          <t>https://www.indeed.com/viewjob?jk=5351eb2f4c376213</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Adhesives Research</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Glen Rock, PA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5351eb2f4c376213</t>
+          <t>https://www.indeed.com/viewjob?jk=3de44fa63b4b67d2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>PAR Technology</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, Spark, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de44fa63b4b67d2</t>
+          <t>https://www.indeed.com/viewjob?jk=c55dd3f9232ba677</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c55dd3f9232ba677</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Camas, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II, Cloud &amp; Web Systems Software</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>Masimo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Camas, WA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Engineer II, Cloud &amp; Web Systems Software</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Masimo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>S3, RDS, Kafka, Snowflake, Time Travel, clustering keys, ETL, ELT, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=df16bce6ff0b45b9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Data Engineer – Remote / Flexible</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Sparklebulb</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>S3, RDS, Kafka, Snowflake, Time Travel, clustering keys, ETL, ELT, Tableau, Tableau Server</t>
+          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df16bce6ff0b45b9</t>
+          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer – Remote / Flexible</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sparklebulb</t>
+          <t>Verkada</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Verkada</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
+          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
+          <t>https://www.indeed.com/viewjob?jk=63c010146ae6d1df</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Senior Data Engineer - Software</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c010146ae6d1df</t>
+          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Software</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
+          <t>https://www.indeed.com/viewjob?jk=80b4ec4ddf5614d5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Allworth Financial</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d2bdc3bf9a8a45</t>
+          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence Data Analyst - GPSC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
+          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Analyst - GPSC</t>
+          <t>Sr Software Developer (Data Agents)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
+          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Software Developer (Data Agents)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hayward, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,52 +2026,52 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
+          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
+          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
+          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Senior Data Scientist + Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>NEOTAX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
+          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Scientist + Machine Learning Engineer</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NEOTAX</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
+          <t>https://www.indeed.com/viewjob?jk=080b9674fa248221</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer (L2) Segment Team</t>
+          <t>Data Engineer (Contract-to-Hire, Part-Time)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>ZENO Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82c7a6b99363103</t>
+          <t>https://www.indeed.com/viewjob?jk=15ed8a390361bf1a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer (Contract-to-Hire, Part-Time)</t>
+          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ZENO Group</t>
+          <t>Intellirent</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Roanoke, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ed8a390361bf1a</t>
+          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Intellirent</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Roanoke, TX, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
+          <t>https://www.indeed.com/viewjob?jk=0d956b2a0c9bb45a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d956b2a0c9bb45a</t>
+          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
+          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Principle Infrastructure Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Paradigm</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Dataflow, Scala, SQL Server, CI/CD, Terraform, Git, Python</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e26a94c5a6adceae</t>
+          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Stelo Support Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>STELO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
+          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Stelo Support Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>STELO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Stelo Support Engineer</t>
+          <t>Data Integration Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>STELO</t>
+          <t>Austin Community College</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
+          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Stelo Support Engineer</t>
+          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>STELO</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2735,76 +2735,6 @@
         </is>
       </c>
       <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Data Integration Developer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Austin Community College</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Paramount Streaming</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2d5d88d53c2ff675</t>
         </is>

--- a/results/job_matches_2026-05-16.xlsx
+++ b/results/job_matches_2026-05-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Platform</t>
+          <t>Microsoft Fabric Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fluency</t>
+          <t>Troutman Pepper Locke</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
+          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Architect</t>
+          <t>Software Engineer 2 ( Backend)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Troutman Pepper Locke</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=020cd3f89e269314</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=020cd3f89e269314</t>
+          <t>https://www.indeed.com/viewjob?jk=bd22044f3d0a4060</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd22044f3d0a4060</t>
+          <t>https://www.indeed.com/viewjob?jk=54e3095eee752df8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer 2 ( Backend)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Biamp Systems</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
+          <t>AWS, IAM, Azure, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e3095eee752df8</t>
+          <t>https://www.indeed.com/viewjob?jk=619b21a83c2def71</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Biamp Systems</t>
+          <t>Fluency</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619b21a83c2def71</t>
+          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Scala, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c55dd3f9232ba677</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Camas, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II, Cloud &amp; Web Systems Software</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>Masimo</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Camas, WA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Engineer II, Cloud &amp; Web Systems Software</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Masimo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>S3, RDS, Kafka, Snowflake, Time Travel, clustering keys, ETL, ELT, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,59 +1686,59 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=df16bce6ff0b45b9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Verkada</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>S3, RDS, Kafka, Snowflake, Time Travel, clustering keys, ETL, ELT, Tableau, Tableau Server</t>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df16bce6ff0b45b9</t>
+          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer – Remote / Flexible</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sparklebulb</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88fa0aa2156f2bd</t>
+          <t>https://www.indeed.com/viewjob?jk=63c010146ae6d1df</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Software</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Verkada</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
+          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c010146ae6d1df</t>
+          <t>https://www.indeed.com/viewjob?jk=80b4ec4ddf5614d5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
+          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Sr Software Developer (Data Agents)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,174 +1886,174 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b4ec4ddf5614d5</t>
+          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
+          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Analyst - GPSC</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8974eee38a514f19</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr Software Developer (Data Agents)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
+          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hayward, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4078c7c96919de98</t>
+          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
+          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,77 +2096,77 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist + Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>NEOTAX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
+          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=080b9674fa248221</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>Data Engineer (Contract-to-Hire, Part-Time)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>ZENO Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=15ed8a390361bf1a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Intellirent</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Roanoke, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
+          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Scientist + Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NEOTAX</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
+          <t>https://www.indeed.com/viewjob?jk=0d956b2a0c9bb45a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>OpenShift Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080b9674fa248221</t>
+          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer (Contract-to-Hire, Part-Time)</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ZENO Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ed8a390361bf1a</t>
+          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Intellirent</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Roanoke, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
+          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d956b2a0c9bb45a</t>
+          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Stelo Support Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>STELO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
+          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Stelo Support Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>STELO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Data Integration Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Onebridge</t>
+          <t>Austin Community College</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Databricks Lakehouse, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c95d8c1b9c6c720</t>
+          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2560,181 +2560,6 @@
         </is>
       </c>
       <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Stelo Support Engineer</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>STELO</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Stelo Support Engineer</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>STELO</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Data Integration Developer</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Austin Community College</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Paramount Streaming</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2d5d88d53c2ff675</t>
         </is>

--- a/results/job_matches_2026-05-16.xlsx
+++ b/results/job_matches_2026-05-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Data Engineer</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Trade Desk</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbbb1cacaaeb3af</t>
+          <t>https://www.indeed.com/viewjob?jk=35842df306ee4c2e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Data Engineer</t>
+          <t>Microsoft Fabric Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Trade Desk</t>
+          <t>Troutman Pepper Locke</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c3dda8a9a898a72</t>
+          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Software Engineer 2 ( Backend)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35842df306ee4c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=020cd3f89e269314</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Architect</t>
+          <t>Software Engineer 2 ( Backend)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Troutman Pepper Locke</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=bd22044f3d0a4060</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=020cd3f89e269314</t>
+          <t>https://www.indeed.com/viewjob?jk=54e3095eee752df8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer 2 ( Backend)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Biamp Systems</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
+          <t>AWS, IAM, Azure, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd22044f3d0a4060</t>
+          <t>https://www.indeed.com/viewjob?jk=619b21a83c2def71</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer 2 ( Backend)</t>
+          <t>Software Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Fluency</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e3095eee752df8</t>
+          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Biamp Systems</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619b21a83c2def71</t>
+          <t>https://www.indeed.com/viewjob?jk=96cb79ea92c31c11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Platform</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fluency</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
+          <t>https://www.indeed.com/viewjob?jk=f15643afd51a012f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cb79ea92c31c11</t>
+          <t>https://www.indeed.com/viewjob?jk=526c7ffc59edd892</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15643afd51a012f</t>
+          <t>https://www.indeed.com/viewjob?jk=3de44fa63b4b67d2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ETL</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526c7ffc59edd892</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Camas, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e7d086f3b943f3</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Infrastructure Engineer</t>
+          <t>Engineer II, Cloud &amp; Web Systems Software</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Masimo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f717e7ca607998f2</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Adhesives Research</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Glen Rock, PA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>S3, RDS, Kafka, Snowflake, Time Travel, clustering keys, ETL, ELT, Tableau, Tableau Server</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5351eb2f4c376213</t>
+          <t>https://www.indeed.com/viewjob?jk=df16bce6ff0b45b9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Verkada</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de44fa63b4b67d2</t>
+          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=63c010146ae6d1df</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Software</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Camas, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Engineer II, Cloud &amp; Web Systems Software</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Masimo</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=80b4ec4ddf5614d5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>S3, RDS, Kafka, Snowflake, Time Travel, clustering keys, ETL, ELT, Tableau, Tableau Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df16bce6ff0b45b9</t>
+          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Software Developer (Data Agents)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Verkada</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,112 +1711,112 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
+          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c010146ae6d1df</t>
+          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Software</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b4ec4ddf5614d5</t>
+          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
+          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr Software Developer (Data Agents)</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
+          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,77 +1921,77 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist + Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>NEOTAX</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
+          <t>https://www.indeed.com/viewjob?jk=080b9674fa248221</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer (Contract-to-Hire, Part-Time)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>ZENO Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=15ed8a390361bf1a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Intellirent</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Roanoke, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
+          <t>https://www.indeed.com/viewjob?jk=0d956b2a0c9bb45a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Scientist + Machine Learning Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NEOTAX</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
+          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>OpenShift Engineer</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080b9674fa248221</t>
+          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer (Contract-to-Hire, Part-Time)</t>
+          <t>Data Integration Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ZENO Group</t>
+          <t>Austin Community College</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ed8a390361bf1a</t>
+          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Intellirent</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Roanoke, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
+          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d956b2a0c9bb45a</t>
+          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Stelo Support Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>STELO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
+          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Stelo Support Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>STELO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2385,181 +2385,6 @@
         </is>
       </c>
       <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Stelo Support Engineer</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>STELO</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Stelo Support Engineer</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>STELO</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Data Integration Developer</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Austin Community College</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Paramount Streaming</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2d5d88d53c2ff675</t>
         </is>

--- a/results/job_matches_2026-05-16.xlsx
+++ b/results/job_matches_2026-05-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Platform, DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,49 +741,49 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62ca3c3ce12832cd</t>
+          <t>https://www.indeed.com/viewjob?jk=10b5742d09907dfe</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Platform, DevOps Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10b5742d09907dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=966e325f5ac56bee</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966e325f5ac56bee</t>
+          <t>https://www.indeed.com/viewjob?jk=64a90374f14eb8a5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>Sr Advanced Cloud Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64a90374f14eb8a5</t>
+          <t>https://www.indeed.com/viewjob?jk=b77fa4bb580f7b02</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Advanced Cloud Developer</t>
+          <t>FullStack AWS AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Event Hubs, GCP, Vertex AI, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77fa4bb580f7b02</t>
+          <t>https://www.indeed.com/viewjob?jk=fe20ccdbad190f18</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FullStack AWS AI Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe20ccdbad190f18</t>
+          <t>https://www.indeed.com/viewjob?jk=248664e537c28c4d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=248664e537c28c4d</t>
+          <t>https://www.indeed.com/viewjob?jk=fd51f4466b978623</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd51f4466b978623</t>
+          <t>https://www.indeed.com/viewjob?jk=35842df306ee4c2e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Microsoft Fabric Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Troutman Pepper Locke</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35842df306ee4c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Architect</t>
+          <t>Software Engineer 2 ( Backend)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Troutman Pepper Locke</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=020cd3f89e269314</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=020cd3f89e269314</t>
+          <t>https://www.indeed.com/viewjob?jk=bd22044f3d0a4060</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd22044f3d0a4060</t>
+          <t>https://www.indeed.com/viewjob?jk=54e3095eee752df8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer 2 ( Backend)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Biamp Systems</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
+          <t>AWS, IAM, Azure, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e3095eee752df8</t>
+          <t>https://www.indeed.com/viewjob?jk=619b21a83c2def71</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Biamp Systems</t>
+          <t>Fluency</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619b21a83c2def71</t>
+          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Platform</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fluency</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
+          <t>https://www.indeed.com/viewjob?jk=96cb79ea92c31c11</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cb79ea92c31c11</t>
+          <t>https://www.indeed.com/viewjob?jk=f15643afd51a012f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15643afd51a012f</t>
+          <t>https://www.indeed.com/viewjob?jk=526c7ffc59edd892</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ETL</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526c7ffc59edd892</t>
+          <t>https://www.indeed.com/viewjob?jk=3de44fa63b4b67d2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de44fa63b4b67d2</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Camas, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II, Cloud &amp; Web Systems Software</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>Masimo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Camas, WA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Engineer II, Cloud &amp; Web Systems Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Masimo</t>
+          <t>Verkada</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>S3, RDS, Kafka, Snowflake, Time Travel, clustering keys, ETL, ELT, Tableau, Tableau Server</t>
+          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df16bce6ff0b45b9</t>
+          <t>https://www.indeed.com/viewjob?jk=63c010146ae6d1df</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Software</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Verkada</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
+          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c010146ae6d1df</t>
+          <t>https://www.indeed.com/viewjob?jk=80b4ec4ddf5614d5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
+          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Sr Software Developer (Data Agents)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,87 +1641,87 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b4ec4ddf5614d5</t>
+          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
+          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Software Developer (Data Agents)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
+          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
+          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>Senior Data Scientist + Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>NEOTAX</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,59 +1896,59 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
+          <t>https://www.indeed.com/viewjob?jk=ac7b41fce729d0ab</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Scientist + Machine Learning Engineer</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NEOTAX</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
+          <t>https://www.indeed.com/viewjob?jk=080b9674fa248221</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>OpenShift Engineer</t>
+          <t>Data Engineer (Contract-to-Hire, Part-Time)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>ZENO Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080b9674fa248221</t>
+          <t>https://www.indeed.com/viewjob?jk=15ed8a390361bf1a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer (Contract-to-Hire, Part-Time)</t>
+          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ZENO Group</t>
+          <t>Intellirent</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Roanoke, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ed8a390361bf1a</t>
+          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Intellirent</t>
+          <t>Montefiore Einstein</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Roanoke, TX, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
+          <t>https://www.indeed.com/viewjob?jk=0d956b2a0c9bb45a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>Mission Pet Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d956b2a0c9bb45a</t>
+          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
+          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Integration Developer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Austin Community College</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Stelo Support Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>STELO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
+          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Stelo Support Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>STELO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Stelo Support Engineer</t>
+          <t>Data Integration Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>STELO</t>
+          <t>Austin Community College</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
+          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Stelo Support Engineer</t>
+          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>STELO</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2350,41 +2350,6 @@
         </is>
       </c>
       <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Paramount Streaming</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2d5d88d53c2ff675</t>
         </is>

--- a/results/job_matches_2026-05-16.xlsx
+++ b/results/job_matches_2026-05-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd51f4466b978623</t>
+          <t>https://www.indeed.com/viewjob?jk=35842df306ee4c2e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Microsoft Fabric Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Troutman Pepper Locke</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35842df306ee4c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Troutman Pepper Locke</t>
+          <t>Biamp Systems</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, IAM, Azure, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=619b21a83c2def71</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Biamp Systems</t>
+          <t>Fluency</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619b21a83c2def71</t>
+          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Platform</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fluency</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
+          <t>https://www.indeed.com/viewjob?jk=526c7ffc59edd892</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cb79ea92c31c11</t>
+          <t>https://www.indeed.com/viewjob?jk=2e2a80dff0ea8242</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Platform Engineer</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15643afd51a012f</t>
+          <t>https://www.indeed.com/viewjob?jk=3de44fa63b4b67d2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ETL</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526c7ffc59edd892</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Camas, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de44fa63b4b67d2</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II, Cloud &amp; Web Systems Software</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>Masimo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>Verkada</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Camas, WA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Engineer II, Cloud &amp; Web Systems Software</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Masimo</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=63c010146ae6d1df</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Software</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Verkada</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
+          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c010146ae6d1df</t>
+          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Software</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
+          <t>https://www.indeed.com/viewjob?jk=80b4ec4ddf5614d5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Sr Software Developer (Data Agents)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,87 +1571,87 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b4ec4ddf5614d5</t>
+          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
+          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Software Developer (Data Agents)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
+          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
+          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,42 +1781,42 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>Senior Data Scientist + Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>NEOTAX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,59 +1826,59 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
+          <t>https://www.indeed.com/viewjob?jk=ac7b41fce729d0ab</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Scientist + Machine Learning Engineer</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NEOTAX</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
+          <t>https://www.indeed.com/viewjob?jk=080b9674fa248221</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer (Contract-to-Hire, Part-Time)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>ZENO Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac7b41fce729d0ab</t>
+          <t>https://www.indeed.com/viewjob?jk=15ed8a390361bf1a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>OpenShift Engineer</t>
+          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Intellirent</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Roanoke, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080b9674fa248221</t>
+          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer (Contract-to-Hire, Part-Time)</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ZENO Group</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ed8a390361bf1a</t>
+          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Intellirent</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Roanoke, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
+          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Montefiore Einstein</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d956b2a0c9bb45a</t>
+          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mission Pet Health</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, ETL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, NoSQL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d32f97f7b35ed04</t>
+          <t>https://www.indeed.com/viewjob?jk=6f160aadc0d3bdd6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Claims Data Analytics Engineer</t>
+          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
+          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5d88d53c2ff675</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Intuitive (Intuitive Surgical)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,182 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Stelo Support Engineer</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>STELO</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=28ccaa21bc08c6c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Stelo Support Engineer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>STELO</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Kafka, Snowflake, Oracle, SQL Server, MySQL</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffc6a461cfb5b0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Data Integration Developer</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Austin Community College</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Hadoop, Oracle, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5779e803082dc4f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Paramount Streaming</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5d88d53c2ff675</t>
+          <t>https://www.indeed.com/viewjob?jk=3677cf32b1561e4d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-16.xlsx
+++ b/results/job_matches_2026-05-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Microsoft Fabric Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Troutman Pepper Locke</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35842df306ee4c2e</t>
+          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Troutman Pepper Locke</t>
+          <t>Biamp Systems</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, IAM, Azure, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492db2dfac4c0f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=619b21a83c2def71</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Biamp Systems</t>
+          <t>Fluency</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, SQL Server, PostgreSQL, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619b21a83c2def71</t>
+          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer 2 ( Backend)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=020cd3f89e269314</t>
+          <t>https://www.indeed.com/viewjob?jk=526c7ffc59edd892</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer 2 ( Backend)</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd22044f3d0a4060</t>
+          <t>https://www.indeed.com/viewjob?jk=3de44fa63b4b67d2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer 2 ( Backend)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, SQL Server, PostgreSQL, Cassandra</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e3095eee752df8</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fluency</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Camas, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, ECS, RDS, Spark, Dask, Polars</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9835c2dd64dde09</t>
+          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Engineer II, Cloud &amp; Web Systems Software</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Masimo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526c7ffc59edd892</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Verkada</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e2a80dff0ea8242</t>
+          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de44fa63b4b67d2</t>
+          <t>https://www.indeed.com/viewjob?jk=63c010146ae6d1df</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Vernon Hills, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee849cf602df7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Developer (Data Agents)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Camas, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Kafka, Oracle, SQL Server, NoSQL, ETL</t>
+          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae7f5047520b4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Engineer II, Cloud &amp; Web Systems Software</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Masimo</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf612beac38dd2c</t>
+          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Verkada</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Airflow, Git</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,102 +1406,102 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89303a4a06cd252</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c010146ae6d1df</t>
+          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Software</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68b44e832eca8f37</t>
+          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Go To Market (Remote)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,102 +1511,102 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4352558a8280bcbb</t>
+          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Data Scientist + Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NEOTAX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b4ec4ddf5614d5</t>
+          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Software Developer (Data Agents)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Data Modeling, ETL, ELT, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326229668d7da82c</t>
+          <t>https://www.indeed.com/viewjob?jk=ac7b41fce729d0ab</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>OpenShift Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47392e37c7d3ad6b</t>
+          <t>https://www.indeed.com/viewjob?jk=080b9674fa248221</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer (Contract-to-Hire, Part-Time)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>ZENO Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5c5bf25b4bcc3b</t>
+          <t>https://www.indeed.com/viewjob?jk=15ed8a390361bf1a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Claims Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35198cc5d5a9abe</t>
+          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6677fe87cb8cb6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer, Go To Market (Remote)</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD, Jenkins, Jenkins, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,427 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65ec96a3a091e0e</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>ETL Data Engineer</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Recutify Inc.</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Spark Streaming, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa84cf8df8c9320</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist + Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>NEOTAX</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Spark, Scala, Python, SQL, Scala</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=219ebfdcbf1c34e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Simplot Company</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac7b41fce729d0ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>OpenShift Engineer</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=080b9674fa248221</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Data Engineer (Contract-to-Hire, Part-Time)</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>ZENO Group</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15ed8a390361bf1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Azure Cloud Operations &amp; AI Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Intellirent</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Roanoke, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13cb7f3467788787</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98496286c254de71</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Edward Jones</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Photon, Scala, ELT, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=4b49c46823fc70a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Claims Data Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Git, Python</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b781c95a46c79e5d</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Sr. Engineer, Machine Learning</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Dayforce</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, NoSQL, ELT, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f160aadc0d3bdd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Experimentation Platform (Backend Services)</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Paramount Streaming</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Redshift, RDS, GCP, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5d88d53c2ff675</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Intuitive (Intuitive Surgical)</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Peachtree Corners, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes, Git, Bitbucket</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3677cf32b1561e4d</t>
         </is>
       </c>
     </row>
